--- a/v2/docs/hospital_canonical.xlsx
+++ b/v2/docs/hospital_canonical.xlsx
@@ -8,6 +8,8 @@
     <sheet name="MechanismEnum" sheetId="3" r:id="rId3"/>
     <sheet name="CategoryAxes" sheetId="4" r:id="rId4"/>
     <sheet name="Legend" sheetId="5" r:id="rId5"/>
+    <sheet name="CategoryBinning_Summary" sheetId="6" r:id="rId6"/>
+    <sheet name="CategoryBinning_Detail" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -402,24 +404,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P160"/>
-  <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="34.83203125" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
-    <col min="4" max="4" width="42.83203125" customWidth="1"/>
-    <col min="5" max="5" width="34.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" customWidth="1"/>
-    <col min="10" max="10" width="50.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-    <col min="14" max="14" width="8.83203125" customWidth="1"/>
-    <col min="15" max="15" width="48.83203125" customWidth="1"/>
-    <col min="16" max="16" width="40.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8431,12 +8415,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D259"/>
-  <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="38.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12074,14 +12052,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F32"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="50.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12733,14 +12703,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F37"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="58.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13492,11 +13454,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C19"/>
-  <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="90.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13712,4 +13669,4921 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H9"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>category</v>
+      </c>
+      <c r="B1" t="str">
+        <v>display_name_en</v>
+      </c>
+      <c r="C1" t="str">
+        <v>canonical_count</v>
+      </c>
+      <c r="D1" t="str">
+        <v>hospital_count_union</v>
+      </c>
+      <c r="E1" t="str">
+        <v>intensity_surgery</v>
+      </c>
+      <c r="F1" t="str">
+        <v>intensity_petit</v>
+      </c>
+      <c r="G1" t="str">
+        <v>intensity_skin</v>
+      </c>
+      <c r="H1" t="str">
+        <v>example_slugs</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>face</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Face</v>
+      </c>
+      <c r="C2">
+        <v>73</v>
+      </c>
+      <c r="D2">
+        <v>16</v>
+      </c>
+      <c r="E2">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>52</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="str">
+        <v>hifu_ulthera, hifu_shurink, hifu_liftera, hifu_linerage, hifu_generic, ...</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Eyes</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="str">
+        <v>skinbooster_rejuran, surgery_eye_double, surgery_eye_shape, surgery_eye_canth_front, surgery_eye_canth_back, ...</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>nose</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Nose</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="str">
+        <v>surgery_nose_hump, surgery_nose_no_implant, surgery_nose_crooked, surgery_nose_contracted, surgery_nose_functional, ...</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>body</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Body</v>
+      </c>
+      <c r="C5">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="str">
+        <v>hifu_body_ultraline, botox_body, filler_shoulder, filler_pelvis, filler_apple_hip, ...</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Skin</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6" t="str">
+        <v>laser_co2, laser_fraxel, laser_pico, laser_genesis, laser_reepot, ...</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>hair</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Hair &amp; Scalp</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <v>exosome_asce, stemcell_hair, prp, hair_transplant</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>wellness</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Wellness &amp; Regenerative</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8" t="str">
+        <v>iv_therapy, stemcell_bio, stemcell_banking, stemcell_joint, cream_firming, ...</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Dental</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9" t="str">
+        <v>dental_implant_oneday, dental_implant_sleep, dental_implant_general, dental_laminate, dental_whitening, ...</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I160"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="38.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>category</v>
+      </c>
+      <c r="B1" t="str">
+        <v>canonical_id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>slug</v>
+      </c>
+      <c r="D1" t="str">
+        <v>name_ko</v>
+      </c>
+      <c r="E1" t="str">
+        <v>name_en</v>
+      </c>
+      <c r="F1" t="str">
+        <v>intensity_tier</v>
+      </c>
+      <c r="G1" t="str">
+        <v>mechanism</v>
+      </c>
+      <c r="H1" t="str">
+        <v>body_areas</v>
+      </c>
+      <c r="I1" t="str">
+        <v>hospital_count</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>face</v>
+      </c>
+      <c r="B2" t="str">
+        <v>CT001</v>
+      </c>
+      <c r="C2" t="str">
+        <v>hifu_ulthera</v>
+      </c>
+      <c r="D2" t="str">
+        <v>울쎄라 (Ulthera)</v>
+      </c>
+      <c r="E2" t="str">
+        <v>HIFU Lifting (Ulthera)</v>
+      </c>
+      <c r="F2" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G2" t="str">
+        <v>hifu</v>
+      </c>
+      <c r="H2" t="str">
+        <v>face,neck</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>face</v>
+      </c>
+      <c r="B3" t="str">
+        <v>CT002</v>
+      </c>
+      <c r="C3" t="str">
+        <v>hifu_shurink</v>
+      </c>
+      <c r="D3" t="str">
+        <v>슈링크 (Shurink)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>HIFU Lifting (Shurink)</v>
+      </c>
+      <c r="F3" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G3" t="str">
+        <v>hifu</v>
+      </c>
+      <c r="H3" t="str">
+        <v>face,neck</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>face</v>
+      </c>
+      <c r="B4" t="str">
+        <v>CT003</v>
+      </c>
+      <c r="C4" t="str">
+        <v>hifu_liftera</v>
+      </c>
+      <c r="D4" t="str">
+        <v>리프테라 (Liftera)</v>
+      </c>
+      <c r="E4" t="str">
+        <v>HIFU Lifting (Liftera)</v>
+      </c>
+      <c r="F4" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G4" t="str">
+        <v>hifu</v>
+      </c>
+      <c r="H4" t="str">
+        <v>face</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>face</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CT004</v>
+      </c>
+      <c r="C5" t="str">
+        <v>hifu_linerage</v>
+      </c>
+      <c r="D5" t="str">
+        <v>리니어지 (Linerage)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>HIFU Lifting (Linerage)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G5" t="str">
+        <v>hifu</v>
+      </c>
+      <c r="H5" t="str">
+        <v>face</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>face</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CT005</v>
+      </c>
+      <c r="C6" t="str">
+        <v>hifu_generic</v>
+      </c>
+      <c r="D6" t="str">
+        <v>HIFU (장비 미명시)</v>
+      </c>
+      <c r="E6" t="str">
+        <v>HIFU (unspecified)</v>
+      </c>
+      <c r="F6" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G6" t="str">
+        <v>hifu</v>
+      </c>
+      <c r="H6" t="str">
+        <v>face</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>face</v>
+      </c>
+      <c r="B7" t="str">
+        <v>CT007</v>
+      </c>
+      <c r="C7" t="str">
+        <v>mmfu_sofwave</v>
+      </c>
+      <c r="D7" t="str">
+        <v>소프웨이브 (Sofwave)</v>
+      </c>
+      <c r="E7" t="str">
+        <v>MMFU (Sofwave)</v>
+      </c>
+      <c r="F7" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G7" t="str">
+        <v>mmfu</v>
+      </c>
+      <c r="H7" t="str">
+        <v>face</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>face</v>
+      </c>
+      <c r="B8" t="str">
+        <v>CT008</v>
+      </c>
+      <c r="C8" t="str">
+        <v>rf_thermage</v>
+      </c>
+      <c r="D8" t="str">
+        <v>써마지 FLX (Thermage)</v>
+      </c>
+      <c r="E8" t="str">
+        <v>RF Lifting (Thermage)</v>
+      </c>
+      <c r="F8" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G8" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H8" t="str">
+        <v>face</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>face</v>
+      </c>
+      <c r="B9" t="str">
+        <v>CT009</v>
+      </c>
+      <c r="C9" t="str">
+        <v>rf_inmode</v>
+      </c>
+      <c r="D9" t="str">
+        <v>인모드 (InMode)</v>
+      </c>
+      <c r="E9" t="str">
+        <v>RF (InMode)</v>
+      </c>
+      <c r="F9" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G9" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H9" t="str">
+        <v>face</v>
+      </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>face</v>
+      </c>
+      <c r="B10" t="str">
+        <v>CT010</v>
+      </c>
+      <c r="C10" t="str">
+        <v>rf_oligio</v>
+      </c>
+      <c r="D10" t="str">
+        <v>올리지오 (Oligio)</v>
+      </c>
+      <c r="E10" t="str">
+        <v>RF (Oligio)</v>
+      </c>
+      <c r="F10" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G10" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H10" t="str">
+        <v>face</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>face</v>
+      </c>
+      <c r="B11" t="str">
+        <v>CT011</v>
+      </c>
+      <c r="C11" t="str">
+        <v>rf_onda</v>
+      </c>
+      <c r="D11" t="str">
+        <v>온다 (Onda)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>RF (Onda)</v>
+      </c>
+      <c r="F11" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G11" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H11" t="str">
+        <v>face,body</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>face</v>
+      </c>
+      <c r="B12" t="str">
+        <v>CT012</v>
+      </c>
+      <c r="C12" t="str">
+        <v>rf_volnewmer</v>
+      </c>
+      <c r="D12" t="str">
+        <v>볼뉴머 (Volnewmer)</v>
+      </c>
+      <c r="E12" t="str">
+        <v>RF (Volnewmer)</v>
+      </c>
+      <c r="F12" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G12" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H12" t="str">
+        <v>face</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>face</v>
+      </c>
+      <c r="B13" t="str">
+        <v>CT013</v>
+      </c>
+      <c r="C13" t="str">
+        <v>rf_coolphase</v>
+      </c>
+      <c r="D13" t="str">
+        <v>쿨페이즈 (Coolphase)</v>
+      </c>
+      <c r="E13" t="str">
+        <v>RF (Coolphase)</v>
+      </c>
+      <c r="F13" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G13" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H13" t="str">
+        <v>face</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>face</v>
+      </c>
+      <c r="B14" t="str">
+        <v>CT014</v>
+      </c>
+      <c r="C14" t="str">
+        <v>rf_titanium</v>
+      </c>
+      <c r="D14" t="str">
+        <v>티타늄 리프팅 (Titanium)</v>
+      </c>
+      <c r="E14" t="str">
+        <v>RF (Titanium)</v>
+      </c>
+      <c r="F14" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G14" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H14" t="str">
+        <v>face</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>face</v>
+      </c>
+      <c r="B15" t="str">
+        <v>CT015</v>
+      </c>
+      <c r="C15" t="str">
+        <v>rf_thor</v>
+      </c>
+      <c r="D15" t="str">
+        <v>토르 (Thor)</v>
+      </c>
+      <c r="E15" t="str">
+        <v>RF (Thor)</v>
+      </c>
+      <c r="F15" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G15" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H15" t="str">
+        <v>face</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>face</v>
+      </c>
+      <c r="B16" t="str">
+        <v>CT016</v>
+      </c>
+      <c r="C16" t="str">
+        <v>rf_belody</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Belody</v>
+      </c>
+      <c r="E16" t="str">
+        <v>RF (Belody)</v>
+      </c>
+      <c r="F16" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G16" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H16" t="str">
+        <v>face</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>face</v>
+      </c>
+      <c r="B17" t="str">
+        <v>CT017</v>
+      </c>
+      <c r="C17" t="str">
+        <v>hifu_rf_combo_ulthermage</v>
+      </c>
+      <c r="D17" t="str">
+        <v>울써마지 (HIFU+RF 콤보)</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Ulthera+Thermage Combo</v>
+      </c>
+      <c r="F17" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G17" t="str">
+        <v>hifu</v>
+      </c>
+      <c r="H17" t="str">
+        <v>face</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>face</v>
+      </c>
+      <c r="B18" t="str">
+        <v>CT018</v>
+      </c>
+      <c r="C18" t="str">
+        <v>rf_microneedle_potenza</v>
+      </c>
+      <c r="D18" t="str">
+        <v>포텐자 (Potenza)</v>
+      </c>
+      <c r="E18" t="str">
+        <v>RF Microneedle (Potenza)</v>
+      </c>
+      <c r="F18" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G18" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H18" t="str">
+        <v>face</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>face</v>
+      </c>
+      <c r="B19" t="str">
+        <v>CT019</v>
+      </c>
+      <c r="C19" t="str">
+        <v>rf_microneedle_morpheus</v>
+      </c>
+      <c r="D19" t="str">
+        <v>모피어스8 (Morpheus8)</v>
+      </c>
+      <c r="E19" t="str">
+        <v>RF Microneedle (Morpheus8)</v>
+      </c>
+      <c r="F19" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G19" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H19" t="str">
+        <v>face</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>face</v>
+      </c>
+      <c r="B20" t="str">
+        <v>CT020</v>
+      </c>
+      <c r="C20" t="str">
+        <v>rf_microneedle_legato</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Legato2</v>
+      </c>
+      <c r="E20" t="str">
+        <v>RF Microneedle (Legato)</v>
+      </c>
+      <c r="F20" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G20" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H20" t="str">
+        <v>face</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>face</v>
+      </c>
+      <c r="B21" t="str">
+        <v>CT036</v>
+      </c>
+      <c r="C21" t="str">
+        <v>botox</v>
+      </c>
+      <c r="D21" t="str">
+        <v>보톡스</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Botox</v>
+      </c>
+      <c r="F21" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G21" t="str">
+        <v>injection_toxin</v>
+      </c>
+      <c r="H21" t="str">
+        <v>face</v>
+      </c>
+      <c r="I21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>face</v>
+      </c>
+      <c r="B22" t="str">
+        <v>CT039</v>
+      </c>
+      <c r="C22" t="str">
+        <v>filler_juvederm</v>
+      </c>
+      <c r="D22" t="str">
+        <v>쥬베덤 (Juvederm)</v>
+      </c>
+      <c r="E22" t="str">
+        <v>HA Filler (Juvederm)</v>
+      </c>
+      <c r="F22" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G22" t="str">
+        <v>injection_filler</v>
+      </c>
+      <c r="H22" t="str">
+        <v>face</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>face</v>
+      </c>
+      <c r="B23" t="str">
+        <v>CT040</v>
+      </c>
+      <c r="C23" t="str">
+        <v>filler_belotero</v>
+      </c>
+      <c r="D23" t="str">
+        <v>벨로테로 (Belotero)</v>
+      </c>
+      <c r="E23" t="str">
+        <v>HA Filler (Belotero)</v>
+      </c>
+      <c r="F23" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G23" t="str">
+        <v>injection_filler</v>
+      </c>
+      <c r="H23" t="str">
+        <v>face</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>face</v>
+      </c>
+      <c r="B24" t="str">
+        <v>CT041</v>
+      </c>
+      <c r="C24" t="str">
+        <v>filler_ellanse</v>
+      </c>
+      <c r="D24" t="str">
+        <v>엘란쎄 (Ellansé)</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Bio-Filler (Ellansé)</v>
+      </c>
+      <c r="F24" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G24" t="str">
+        <v>injection_filler</v>
+      </c>
+      <c r="H24" t="str">
+        <v>face</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>face</v>
+      </c>
+      <c r="B25" t="str">
+        <v>CT042</v>
+      </c>
+      <c r="C25" t="str">
+        <v>filler_neauvia</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Neauvia 필러</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Bio-Filler (Neauvia)</v>
+      </c>
+      <c r="F25" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G25" t="str">
+        <v>injection_filler</v>
+      </c>
+      <c r="H25" t="str">
+        <v>face</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>face</v>
+      </c>
+      <c r="B26" t="str">
+        <v>CT043</v>
+      </c>
+      <c r="C26" t="str">
+        <v>filler_face_generic</v>
+      </c>
+      <c r="D26" t="str">
+        <v>필러 (얼굴, generic)</v>
+      </c>
+      <c r="E26" t="str">
+        <v>HA Filler (Generic, Face)</v>
+      </c>
+      <c r="F26" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G26" t="str">
+        <v>injection_filler</v>
+      </c>
+      <c r="H26" t="str">
+        <v>face</v>
+      </c>
+      <c r="I26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>face</v>
+      </c>
+      <c r="B27" t="str">
+        <v>CT047</v>
+      </c>
+      <c r="C27" t="str">
+        <v>filler_ear</v>
+      </c>
+      <c r="D27" t="str">
+        <v>귀 필러</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Ear Filler</v>
+      </c>
+      <c r="F27" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G27" t="str">
+        <v>injection_filler</v>
+      </c>
+      <c r="H27" t="str">
+        <v>ear</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>face</v>
+      </c>
+      <c r="B28" t="str">
+        <v>CT049</v>
+      </c>
+      <c r="C28" t="str">
+        <v>skinbooster_juvelook</v>
+      </c>
+      <c r="D28" t="str">
+        <v>쥬베룩 (Juvelook)</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Skin Booster (Juvelook)</v>
+      </c>
+      <c r="F28" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G28" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H28" t="str">
+        <v>face</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>face</v>
+      </c>
+      <c r="B29" t="str">
+        <v>CT050</v>
+      </c>
+      <c r="C29" t="str">
+        <v>skinbooster_skinvive</v>
+      </c>
+      <c r="D29" t="str">
+        <v>스킨바이브 (Skinvive)</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Skin Booster (Skinvive)</v>
+      </c>
+      <c r="F29" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G29" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H29" t="str">
+        <v>face</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>face</v>
+      </c>
+      <c r="B30" t="str">
+        <v>CT051</v>
+      </c>
+      <c r="C30" t="str">
+        <v>skinbooster_lumivion</v>
+      </c>
+      <c r="D30" t="str">
+        <v>루미비온 (Lumivion)</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Skin Booster (Lumivion)</v>
+      </c>
+      <c r="F30" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G30" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H30" t="str">
+        <v>face</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>face</v>
+      </c>
+      <c r="B31" t="str">
+        <v>CT052</v>
+      </c>
+      <c r="C31" t="str">
+        <v>skinbooster_elebes</v>
+      </c>
+      <c r="D31" t="str">
+        <v>엘레베스 (Elebes)</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Skin Booster (Elebes)</v>
+      </c>
+      <c r="F31" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G31" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H31" t="str">
+        <v>face</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>face</v>
+      </c>
+      <c r="B32" t="str">
+        <v>CT053</v>
+      </c>
+      <c r="C32" t="str">
+        <v>skinbooster_metacell</v>
+      </c>
+      <c r="D32" t="str">
+        <v>메타셀 MCT</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Skin Booster (MetaCell MCT)</v>
+      </c>
+      <c r="F32" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G32" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H32" t="str">
+        <v>face</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>face</v>
+      </c>
+      <c r="B33" t="str">
+        <v>CT054</v>
+      </c>
+      <c r="C33" t="str">
+        <v>skinbooster_rizene</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Rizene</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Skin Booster (Rizene)</v>
+      </c>
+      <c r="F33" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G33" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H33" t="str">
+        <v>face</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>face</v>
+      </c>
+      <c r="B34" t="str">
+        <v>CT055</v>
+      </c>
+      <c r="C34" t="str">
+        <v>skinbooster_relead</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Relead M</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Skin Booster (Relead M)</v>
+      </c>
+      <c r="F34" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G34" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H34" t="str">
+        <v>face</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>face</v>
+      </c>
+      <c r="B35" t="str">
+        <v>CT056</v>
+      </c>
+      <c r="C35" t="str">
+        <v>skinbooster_rebirth</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Rebirth Booster</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Rebirth Booster (AYUN)</v>
+      </c>
+      <c r="F35" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G35" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H35" t="str">
+        <v>face</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>face</v>
+      </c>
+      <c r="B36" t="str">
+        <v>CT057</v>
+      </c>
+      <c r="C36" t="str">
+        <v>skinbooster_generic</v>
+      </c>
+      <c r="D36" t="str">
+        <v>스킨부스터 / 콜라겐부스터 (generic)</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Skin / Collagen Booster (Generic)</v>
+      </c>
+      <c r="F36" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G36" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H36" t="str">
+        <v>face</v>
+      </c>
+      <c r="I36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>face</v>
+      </c>
+      <c r="B37" t="str">
+        <v>CT058</v>
+      </c>
+      <c r="C37" t="str">
+        <v>collagen_sculptra</v>
+      </c>
+      <c r="D37" t="str">
+        <v>스컬트라 (Sculptra)</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Collagen Booster (Sculptra)</v>
+      </c>
+      <c r="F37" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G37" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H37" t="str">
+        <v>face</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>face</v>
+      </c>
+      <c r="B38" t="str">
+        <v>CT061</v>
+      </c>
+      <c r="C38" t="str">
+        <v>injection_violet</v>
+      </c>
+      <c r="D38" t="str">
+        <v>브이올렛 주사</v>
+      </c>
+      <c r="E38" t="str">
+        <v>V-let Injection</v>
+      </c>
+      <c r="F38" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G38" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H38" t="str">
+        <v>face</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>face</v>
+      </c>
+      <c r="B39" t="str">
+        <v>CT062</v>
+      </c>
+      <c r="C39" t="str">
+        <v>injection_liencell_skin</v>
+      </c>
+      <c r="D39" t="str">
+        <v>리엔셀 피부주사</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Liencell Skin Injection</v>
+      </c>
+      <c r="F39" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G39" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H39" t="str">
+        <v>face</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>face</v>
+      </c>
+      <c r="B40" t="str">
+        <v>CT063</v>
+      </c>
+      <c r="C40" t="str">
+        <v>injection_lifting</v>
+      </c>
+      <c r="D40" t="str">
+        <v>리프팅 주사</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Lifting Injection</v>
+      </c>
+      <c r="F40" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G40" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H40" t="str">
+        <v>face</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>face</v>
+      </c>
+      <c r="B41" t="str">
+        <v>CT066</v>
+      </c>
+      <c r="C41" t="str">
+        <v>thread_silhouette</v>
+      </c>
+      <c r="D41" t="str">
+        <v>실루엣 소프트 (PLA)</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Silhouette Soft (PLA 360°)</v>
+      </c>
+      <c r="F41" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G41" t="str">
+        <v>thread</v>
+      </c>
+      <c r="H41" t="str">
+        <v>face</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>face</v>
+      </c>
+      <c r="B42" t="str">
+        <v>CT067</v>
+      </c>
+      <c r="C42" t="str">
+        <v>thread_mint</v>
+      </c>
+      <c r="D42" t="str">
+        <v>민트리프팅 (PCL)</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Mint Lift (PCL)</v>
+      </c>
+      <c r="F42" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G42" t="str">
+        <v>thread</v>
+      </c>
+      <c r="H42" t="str">
+        <v>face</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>face</v>
+      </c>
+      <c r="B43" t="str">
+        <v>CT068</v>
+      </c>
+      <c r="C43" t="str">
+        <v>thread_elasticum</v>
+      </c>
+      <c r="D43" t="str">
+        <v>엘라스티꿈 리프팅</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Elasticum Lift</v>
+      </c>
+      <c r="F43" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G43" t="str">
+        <v>thread</v>
+      </c>
+      <c r="H43" t="str">
+        <v>face</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>face</v>
+      </c>
+      <c r="B44" t="str">
+        <v>CT069</v>
+      </c>
+      <c r="C44" t="str">
+        <v>thread_wonder</v>
+      </c>
+      <c r="D44" t="str">
+        <v>원더 리프팅</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Wonder Lift</v>
+      </c>
+      <c r="F44" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G44" t="str">
+        <v>thread</v>
+      </c>
+      <c r="H44" t="str">
+        <v>face</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>face</v>
+      </c>
+      <c r="B45" t="str">
+        <v>CT070</v>
+      </c>
+      <c r="C45" t="str">
+        <v>thread_aptos</v>
+      </c>
+      <c r="D45" t="str">
+        <v>압토스 (Aptos)</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Aptos Thread</v>
+      </c>
+      <c r="F45" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G45" t="str">
+        <v>thread</v>
+      </c>
+      <c r="H45" t="str">
+        <v>jawline,neck</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>face</v>
+      </c>
+      <c r="B46" t="str">
+        <v>CT071</v>
+      </c>
+      <c r="C46" t="str">
+        <v>thread_epiticon</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Epiticon</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Epiticon Thread</v>
+      </c>
+      <c r="F46" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G46" t="str">
+        <v>thread</v>
+      </c>
+      <c r="H46" t="str">
+        <v>face</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>face</v>
+      </c>
+      <c r="B47" t="str">
+        <v>CT072</v>
+      </c>
+      <c r="C47" t="str">
+        <v>thread_mini_smas</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Mini SMAS Thread</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Mini SMAS Thread</v>
+      </c>
+      <c r="F47" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G47" t="str">
+        <v>thread</v>
+      </c>
+      <c r="H47" t="str">
+        <v>face</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>face</v>
+      </c>
+      <c r="B48" t="str">
+        <v>CT073</v>
+      </c>
+      <c r="C48" t="str">
+        <v>thread_generic</v>
+      </c>
+      <c r="D48" t="str">
+        <v>실리프팅 (generic)</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Thread Lift (Generic)</v>
+      </c>
+      <c r="F48" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G48" t="str">
+        <v>thread</v>
+      </c>
+      <c r="H48" t="str">
+        <v>face</v>
+      </c>
+      <c r="I48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>face</v>
+      </c>
+      <c r="B49" t="str">
+        <v>CT080</v>
+      </c>
+      <c r="C49" t="str">
+        <v>stemcell_antiaging</v>
+      </c>
+      <c r="D49" t="str">
+        <v>줄기세포 항노화 (얼굴)</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Anti-aging Stem Cell</v>
+      </c>
+      <c r="F49" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G49" t="str">
+        <v>stem_cell</v>
+      </c>
+      <c r="H49" t="str">
+        <v>face</v>
+      </c>
+      <c r="I49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>face</v>
+      </c>
+      <c r="B50" t="str">
+        <v>CT081</v>
+      </c>
+      <c r="C50" t="str">
+        <v>stemcell_skin_shot</v>
+      </c>
+      <c r="D50" t="str">
+        <v>지방줄기세포 스킨샷</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Stem Cell Skin Shot</v>
+      </c>
+      <c r="F50" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G50" t="str">
+        <v>stem_cell</v>
+      </c>
+      <c r="H50" t="str">
+        <v>face</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>face</v>
+      </c>
+      <c r="B51" t="str">
+        <v>CT099</v>
+      </c>
+      <c r="C51" t="str">
+        <v>lifting_unspecified</v>
+      </c>
+      <c r="D51" t="str">
+        <v>리프팅 (기기 미명시)</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Lifting (Unspecified)</v>
+      </c>
+      <c r="F51" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G51" t="str">
+        <v>hifu</v>
+      </c>
+      <c r="H51" t="str">
+        <v>face</v>
+      </c>
+      <c r="I51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>face</v>
+      </c>
+      <c r="B52" t="str">
+        <v>CT117</v>
+      </c>
+      <c r="C52" t="str">
+        <v>surgery_jaw_vline</v>
+      </c>
+      <c r="D52" t="str">
+        <v>V라인 (사각턱 축소)</v>
+      </c>
+      <c r="E52" t="str">
+        <v>V-line Jaw</v>
+      </c>
+      <c r="F52" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G52" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H52" t="str">
+        <v>jaw</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>face</v>
+      </c>
+      <c r="B53" t="str">
+        <v>CT118</v>
+      </c>
+      <c r="C53" t="str">
+        <v>surgery_jaw_mandible</v>
+      </c>
+      <c r="D53" t="str">
+        <v>사각턱 축소</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Mandible Reduction</v>
+      </c>
+      <c r="F53" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G53" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H53" t="str">
+        <v>jaw</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>face</v>
+      </c>
+      <c r="B54" t="str">
+        <v>CT119</v>
+      </c>
+      <c r="C54" t="str">
+        <v>surgery_zygoma</v>
+      </c>
+      <c r="D54" t="str">
+        <v>광대 축소</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Zygoma Reduction</v>
+      </c>
+      <c r="F54" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G54" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H54" t="str">
+        <v>cheek</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>face</v>
+      </c>
+      <c r="B55" t="str">
+        <v>CT122</v>
+      </c>
+      <c r="C55" t="str">
+        <v>surgery_lift_facelift</v>
+      </c>
+      <c r="D55" t="str">
+        <v>안면거상</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Facelift</v>
+      </c>
+      <c r="F55" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G55" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H55" t="str">
+        <v>face</v>
+      </c>
+      <c r="I55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>face</v>
+      </c>
+      <c r="B56" t="str">
+        <v>CT123</v>
+      </c>
+      <c r="C56" t="str">
+        <v>surgery_lift_smas</v>
+      </c>
+      <c r="D56" t="str">
+        <v>SMAS 리프트</v>
+      </c>
+      <c r="E56" t="str">
+        <v>SMAS Lift</v>
+      </c>
+      <c r="F56" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G56" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H56" t="str">
+        <v>face</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>face</v>
+      </c>
+      <c r="B57" t="str">
+        <v>CT124</v>
+      </c>
+      <c r="C57" t="str">
+        <v>surgery_lift_miniquick</v>
+      </c>
+      <c r="D57" t="str">
+        <v>미니퀵 리프팅</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Mini Quick Lift</v>
+      </c>
+      <c r="F57" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G57" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H57" t="str">
+        <v>face</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>face</v>
+      </c>
+      <c r="B58" t="str">
+        <v>CT125</v>
+      </c>
+      <c r="C58" t="str">
+        <v>surgery_lift_forehead</v>
+      </c>
+      <c r="D58" t="str">
+        <v>이마거상</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Forehead Lift</v>
+      </c>
+      <c r="F58" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G58" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H58" t="str">
+        <v>forehead</v>
+      </c>
+      <c r="I58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>face</v>
+      </c>
+      <c r="B59" t="str">
+        <v>CT126</v>
+      </c>
+      <c r="C59" t="str">
+        <v>surgery_lift_midface</v>
+      </c>
+      <c r="D59" t="str">
+        <v>하안검·미드페이스리프트</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Lower Bleph + Midface Lift</v>
+      </c>
+      <c r="F59" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G59" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H59" t="str">
+        <v>face</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>face</v>
+      </c>
+      <c r="B60" t="str">
+        <v>CT127</v>
+      </c>
+      <c r="C60" t="str">
+        <v>surgery_lift_neck</v>
+      </c>
+      <c r="D60" t="str">
+        <v>목거상</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Neck Lift</v>
+      </c>
+      <c r="F60" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G60" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H60" t="str">
+        <v>neck</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>face</v>
+      </c>
+      <c r="B61" t="str">
+        <v>CT128</v>
+      </c>
+      <c r="C61" t="str">
+        <v>surgery_lip_philtrum</v>
+      </c>
+      <c r="D61" t="str">
+        <v>인중성형</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Philtrum Surgery</v>
+      </c>
+      <c r="F61" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G61" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H61" t="str">
+        <v>lip</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>face</v>
+      </c>
+      <c r="B62" t="str">
+        <v>CT129</v>
+      </c>
+      <c r="C62" t="str">
+        <v>surgery_lip_reduction</v>
+      </c>
+      <c r="D62" t="str">
+        <v>입술축소</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Lip Reduction</v>
+      </c>
+      <c r="F62" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G62" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H62" t="str">
+        <v>lip</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>face</v>
+      </c>
+      <c r="B63" t="str">
+        <v>CT130</v>
+      </c>
+      <c r="C63" t="str">
+        <v>surgery_lip_general</v>
+      </c>
+      <c r="D63" t="str">
+        <v>입술성형 (일반)</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Lip Surgery (General)</v>
+      </c>
+      <c r="F63" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G63" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H63" t="str">
+        <v>lip</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>face</v>
+      </c>
+      <c r="B64" t="str">
+        <v>CT131</v>
+      </c>
+      <c r="C64" t="str">
+        <v>surgery_cleft_lip</v>
+      </c>
+      <c r="D64" t="str">
+        <v>구순열 성형 (Cleft Lip)</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Cleft Lip Repair</v>
+      </c>
+      <c r="F64" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G64" t="str">
+        <v>reconstructive</v>
+      </c>
+      <c r="H64" t="str">
+        <v>lip</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>face</v>
+      </c>
+      <c r="B65" t="str">
+        <v>CT132</v>
+      </c>
+      <c r="C65" t="str">
+        <v>surgery_cleft_palate</v>
+      </c>
+      <c r="D65" t="str">
+        <v>구순구개열 2차 (Cleft Lip &amp; Palate)</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Cleft Lip &amp; Palate Revision</v>
+      </c>
+      <c r="F65" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G65" t="str">
+        <v>reconstructive</v>
+      </c>
+      <c r="H65" t="str">
+        <v>lip,nose</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>face</v>
+      </c>
+      <c r="B66" t="str">
+        <v>CT133</v>
+      </c>
+      <c r="C66" t="str">
+        <v>surgery_scar_revision</v>
+      </c>
+      <c r="D66" t="str">
+        <v>흉터 성형</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Scar Revision</v>
+      </c>
+      <c r="F66" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G66" t="str">
+        <v>reconstructive</v>
+      </c>
+      <c r="H66" t="str">
+        <v>skin</v>
+      </c>
+      <c r="I66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>face</v>
+      </c>
+      <c r="B67" t="str">
+        <v>CT134</v>
+      </c>
+      <c r="C67" t="str">
+        <v>surgery_burn</v>
+      </c>
+      <c r="D67" t="str">
+        <v>화상 치료</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Burn Treatment</v>
+      </c>
+      <c r="F67" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G67" t="str">
+        <v>reconstructive</v>
+      </c>
+      <c r="H67" t="str">
+        <v>skin</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>face</v>
+      </c>
+      <c r="B68" t="str">
+        <v>CT135</v>
+      </c>
+      <c r="C68" t="str">
+        <v>surgery_foreign_body</v>
+      </c>
+      <c r="D68" t="str">
+        <v>이물 제거</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Foreign Body Removal</v>
+      </c>
+      <c r="F68" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G68" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H68" t="str">
+        <v>face,body</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>face</v>
+      </c>
+      <c r="B69" t="str">
+        <v>CT136</v>
+      </c>
+      <c r="C69" t="str">
+        <v>surgery_forehead_red</v>
+      </c>
+      <c r="D69" t="str">
+        <v>이마축소 (헤어라인)</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Forehead Reduction</v>
+      </c>
+      <c r="F69" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G69" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H69" t="str">
+        <v>forehead</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>face</v>
+      </c>
+      <c r="B70" t="str">
+        <v>CT138</v>
+      </c>
+      <c r="C70" t="str">
+        <v>surgery_earlobe</v>
+      </c>
+      <c r="D70" t="str">
+        <v>귓불 교정</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Earlobe Correction</v>
+      </c>
+      <c r="F70" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G70" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H70" t="str">
+        <v>ear</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>face</v>
+      </c>
+      <c r="B71" t="str">
+        <v>CT142</v>
+      </c>
+      <c r="C71" t="str">
+        <v>surgery_body_contour</v>
+      </c>
+      <c r="D71" t="str">
+        <v>바디 컨투어 수술</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Body Contouring Surgery</v>
+      </c>
+      <c r="F71" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G71" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H71" t="str">
+        <v>body</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>face</v>
+      </c>
+      <c r="B72" t="str">
+        <v>CT143</v>
+      </c>
+      <c r="C72" t="str">
+        <v>surgery_forehead_general</v>
+      </c>
+      <c r="D72" t="str">
+        <v>이마 성형 (일반)</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Forehead Surgery (General)</v>
+      </c>
+      <c r="F72" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G72" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H72" t="str">
+        <v>forehead</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>face</v>
+      </c>
+      <c r="B73" t="str">
+        <v>CT146</v>
+      </c>
+      <c r="C73" t="str">
+        <v>bundle_salondrtunes_juvenile</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Salon de Juvénile (줄기세포 프로그램)</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Salon de Juvénile (Stem Cell Program)</v>
+      </c>
+      <c r="F73" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G73" t="str">
+        <v>stem_cell</v>
+      </c>
+      <c r="H73" t="str">
+        <v>systemic,face</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>face</v>
+      </c>
+      <c r="B74" t="str">
+        <v>CT147</v>
+      </c>
+      <c r="C74" t="str">
+        <v>bundle_salondrtunes_alllayer</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Salon de All-Layer (리프팅 프로그램)</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Salon de All-Layer (Lifting Program)</v>
+      </c>
+      <c r="F74" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G74" t="str">
+        <v>hifu</v>
+      </c>
+      <c r="H74" t="str">
+        <v>face</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B75" t="str">
+        <v>CT048</v>
+      </c>
+      <c r="C75" t="str">
+        <v>skinbooster_rejuran</v>
+      </c>
+      <c r="D75" t="str">
+        <v>리쥬란 (Rejuran)</v>
+      </c>
+      <c r="E75" t="str">
+        <v>PN Skin Booster (Rejuran)</v>
+      </c>
+      <c r="F75" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G75" t="str">
+        <v>injection_skin</v>
+      </c>
+      <c r="H75" t="str">
+        <v>face,eye</v>
+      </c>
+      <c r="I75">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B76" t="str">
+        <v>CT101</v>
+      </c>
+      <c r="C76" t="str">
+        <v>surgery_eye_double</v>
+      </c>
+      <c r="D76" t="str">
+        <v>쌍커풀 수술</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Double Eyelid Surgery</v>
+      </c>
+      <c r="F76" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G76" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H76" t="str">
+        <v>eye</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B77" t="str">
+        <v>CT102</v>
+      </c>
+      <c r="C77" t="str">
+        <v>surgery_eye_shape</v>
+      </c>
+      <c r="D77" t="str">
+        <v>눈매교정</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Eye Shape Correction (Ptosis)</v>
+      </c>
+      <c r="F77" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G77" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H77" t="str">
+        <v>eye</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B78" t="str">
+        <v>CT103</v>
+      </c>
+      <c r="C78" t="str">
+        <v>surgery_eye_canth_front</v>
+      </c>
+      <c r="D78" t="str">
+        <v>앞트임</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Epicanthoplasty (Inner Corner)</v>
+      </c>
+      <c r="F78" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G78" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H78" t="str">
+        <v>eye</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B79" t="str">
+        <v>CT104</v>
+      </c>
+      <c r="C79" t="str">
+        <v>surgery_eye_canth_back</v>
+      </c>
+      <c r="D79" t="str">
+        <v>뒤트임</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Lateral Canthoplasty (Outer Corner)</v>
+      </c>
+      <c r="F79" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G79" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H79" t="str">
+        <v>eye</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B80" t="str">
+        <v>CT105</v>
+      </c>
+      <c r="C80" t="str">
+        <v>surgery_eye_lower</v>
+      </c>
+      <c r="D80" t="str">
+        <v>눈밑지방재배치</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Lower Blepharoplasty</v>
+      </c>
+      <c r="F80" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G80" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H80" t="str">
+        <v>eye</v>
+      </c>
+      <c r="I80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B81" t="str">
+        <v>CT106</v>
+      </c>
+      <c r="C81" t="str">
+        <v>surgery_eye_blepharo</v>
+      </c>
+      <c r="D81" t="str">
+        <v>안검 성형 (일반)</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Blepharoplasty (General)</v>
+      </c>
+      <c r="F81" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G81" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H81" t="str">
+        <v>eye</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B82" t="str">
+        <v>CT107</v>
+      </c>
+      <c r="C82" t="str">
+        <v>surgery_eye_bag</v>
+      </c>
+      <c r="D82" t="str">
+        <v>안검 지방 제거</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Eye Bag Removal</v>
+      </c>
+      <c r="F82" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G82" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H82" t="str">
+        <v>eye</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B83" t="str">
+        <v>CT108</v>
+      </c>
+      <c r="C83" t="str">
+        <v>surgery_eye_subbrow</v>
+      </c>
+      <c r="D83" t="str">
+        <v>눈썹·상안검 거상</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Sub-brow / Upper Bleph Lift</v>
+      </c>
+      <c r="F83" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G83" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H83" t="str">
+        <v>eye,brow</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B84" t="str">
+        <v>CT109</v>
+      </c>
+      <c r="C84" t="str">
+        <v>surgery_eye_wooatrim</v>
+      </c>
+      <c r="D84" t="str">
+        <v>우아트임 (WOOA signature)</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Wooa Eye Cut (Signature)</v>
+      </c>
+      <c r="F84" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G84" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H84" t="str">
+        <v>eye</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>eyes</v>
+      </c>
+      <c r="B85" t="str">
+        <v>CT159</v>
+      </c>
+      <c r="C85" t="str">
+        <v>surgery_eye_general</v>
+      </c>
+      <c r="D85" t="str">
+        <v>눈 성형 (일반)</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Eye Surgery (General)</v>
+      </c>
+      <c r="F85" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G85" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H85" t="str">
+        <v>eye</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>nose</v>
+      </c>
+      <c r="B86" t="str">
+        <v>CT110</v>
+      </c>
+      <c r="C86" t="str">
+        <v>surgery_nose_hump</v>
+      </c>
+      <c r="D86" t="str">
+        <v>매부리코</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Hump Nose</v>
+      </c>
+      <c r="F86" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G86" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H86" t="str">
+        <v>nose</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>nose</v>
+      </c>
+      <c r="B87" t="str">
+        <v>CT111</v>
+      </c>
+      <c r="C87" t="str">
+        <v>surgery_nose_no_implant</v>
+      </c>
+      <c r="D87" t="str">
+        <v>무보형물 코성형</v>
+      </c>
+      <c r="E87" t="str">
+        <v>No-implant Rhinoplasty</v>
+      </c>
+      <c r="F87" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G87" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H87" t="str">
+        <v>nose</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>nose</v>
+      </c>
+      <c r="B88" t="str">
+        <v>CT112</v>
+      </c>
+      <c r="C88" t="str">
+        <v>surgery_nose_crooked</v>
+      </c>
+      <c r="D88" t="str">
+        <v>휜코 (Crooked Nose)</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Crooked Nose</v>
+      </c>
+      <c r="F88" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G88" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H88" t="str">
+        <v>nose</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>nose</v>
+      </c>
+      <c r="B89" t="str">
+        <v>CT113</v>
+      </c>
+      <c r="C89" t="str">
+        <v>surgery_nose_contracted</v>
+      </c>
+      <c r="D89" t="str">
+        <v>구축코 재수술</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Contracted Nose Revision</v>
+      </c>
+      <c r="F89" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G89" t="str">
+        <v>reconstructive</v>
+      </c>
+      <c r="H89" t="str">
+        <v>nose</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>nose</v>
+      </c>
+      <c r="B90" t="str">
+        <v>CT114</v>
+      </c>
+      <c r="C90" t="str">
+        <v>surgery_nose_functional</v>
+      </c>
+      <c r="D90" t="str">
+        <v>기능코성형</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Functional Rhinoplasty</v>
+      </c>
+      <c r="F90" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G90" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H90" t="str">
+        <v>nose</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>nose</v>
+      </c>
+      <c r="B91" t="str">
+        <v>CT115</v>
+      </c>
+      <c r="C91" t="str">
+        <v>surgery_nose_asymmetry</v>
+      </c>
+      <c r="D91" t="str">
+        <v>콧구멍 비대칭 교정</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Nostril Asymmetry Correction</v>
+      </c>
+      <c r="F91" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G91" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H91" t="str">
+        <v>nose</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>nose</v>
+      </c>
+      <c r="B92" t="str">
+        <v>CT116</v>
+      </c>
+      <c r="C92" t="str">
+        <v>surgery_nose_general</v>
+      </c>
+      <c r="D92" t="str">
+        <v>코성형 (일반)</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Rhinoplasty (General)</v>
+      </c>
+      <c r="F92" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G92" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H92" t="str">
+        <v>nose</v>
+      </c>
+      <c r="I92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>body</v>
+      </c>
+      <c r="B93" t="str">
+        <v>CT006</v>
+      </c>
+      <c r="C93" t="str">
+        <v>hifu_body_ultraline</v>
+      </c>
+      <c r="D93" t="str">
+        <v>울트라인 (Body HIFU)</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Body HIFU (Ultraline)</v>
+      </c>
+      <c r="F93" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G93" t="str">
+        <v>hifu</v>
+      </c>
+      <c r="H93" t="str">
+        <v>body</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>body</v>
+      </c>
+      <c r="B94" t="str">
+        <v>CT037</v>
+      </c>
+      <c r="C94" t="str">
+        <v>botox_body</v>
+      </c>
+      <c r="D94" t="str">
+        <v>바디 보툴리늄</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Body Botox</v>
+      </c>
+      <c r="F94" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G94" t="str">
+        <v>injection_toxin</v>
+      </c>
+      <c r="H94" t="str">
+        <v>body,shoulder,calf</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>body</v>
+      </c>
+      <c r="B95" t="str">
+        <v>CT044</v>
+      </c>
+      <c r="C95" t="str">
+        <v>filler_shoulder</v>
+      </c>
+      <c r="D95" t="str">
+        <v>직각 어깨 필러</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Shoulder Filler (Body Contouring)</v>
+      </c>
+      <c r="F95" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G95" t="str">
+        <v>injection_filler</v>
+      </c>
+      <c r="H95" t="str">
+        <v>shoulder</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>body</v>
+      </c>
+      <c r="B96" t="str">
+        <v>CT045</v>
+      </c>
+      <c r="C96" t="str">
+        <v>filler_pelvis</v>
+      </c>
+      <c r="D96" t="str">
+        <v>골반 필러</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Pelvis Filler</v>
+      </c>
+      <c r="F96" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G96" t="str">
+        <v>injection_filler</v>
+      </c>
+      <c r="H96" t="str">
+        <v>pelvis</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>body</v>
+      </c>
+      <c r="B97" t="str">
+        <v>CT046</v>
+      </c>
+      <c r="C97" t="str">
+        <v>filler_apple_hip</v>
+      </c>
+      <c r="D97" t="str">
+        <v>애플힙 필러</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Apple Hip Filler</v>
+      </c>
+      <c r="F97" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G97" t="str">
+        <v>injection_filler</v>
+      </c>
+      <c r="H97" t="str">
+        <v>buttocks</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>body</v>
+      </c>
+      <c r="B98" t="str">
+        <v>CT060</v>
+      </c>
+      <c r="C98" t="str">
+        <v>injection_contour</v>
+      </c>
+      <c r="D98" t="str">
+        <v>윤곽 주사</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Lipolytic Contour Injection</v>
+      </c>
+      <c r="F98" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G98" t="str">
+        <v>fat_dissolve_injection</v>
+      </c>
+      <c r="H98" t="str">
+        <v>face</v>
+      </c>
+      <c r="I98">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>body</v>
+      </c>
+      <c r="B99" t="str">
+        <v>CT064</v>
+      </c>
+      <c r="C99" t="str">
+        <v>fatdissolve_face_body</v>
+      </c>
+      <c r="D99" t="str">
+        <v>지방분해 주사 (DCA/카복시/MTS)</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Fat-dissolving Injection</v>
+      </c>
+      <c r="F99" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G99" t="str">
+        <v>fat_dissolve_injection</v>
+      </c>
+      <c r="H99" t="str">
+        <v>face,body,arm,thigh,abdomen</v>
+      </c>
+      <c r="I99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>body</v>
+      </c>
+      <c r="B100" t="str">
+        <v>CT087</v>
+      </c>
+      <c r="C100" t="str">
+        <v>lipo_face</v>
+      </c>
+      <c r="D100" t="str">
+        <v>안면 지방흡입</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Facial Liposuction</v>
+      </c>
+      <c r="F100" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G100" t="str">
+        <v>liposuction</v>
+      </c>
+      <c r="H100" t="str">
+        <v>face</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>body</v>
+      </c>
+      <c r="B101" t="str">
+        <v>CT088</v>
+      </c>
+      <c r="C101" t="str">
+        <v>lipo_abdomen</v>
+      </c>
+      <c r="D101" t="str">
+        <v>복부 지방흡입</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Abdomen Liposuction</v>
+      </c>
+      <c r="F101" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G101" t="str">
+        <v>liposuction</v>
+      </c>
+      <c r="H101" t="str">
+        <v>abdomen</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>body</v>
+      </c>
+      <c r="B102" t="str">
+        <v>CT089</v>
+      </c>
+      <c r="C102" t="str">
+        <v>lipo_thigh</v>
+      </c>
+      <c r="D102" t="str">
+        <v>허벅지 지방흡입</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Thigh Liposuction</v>
+      </c>
+      <c r="F102" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G102" t="str">
+        <v>liposuction</v>
+      </c>
+      <c r="H102" t="str">
+        <v>thigh</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>body</v>
+      </c>
+      <c r="B103" t="str">
+        <v>CT090</v>
+      </c>
+      <c r="C103" t="str">
+        <v>lipo_arm</v>
+      </c>
+      <c r="D103" t="str">
+        <v>팔뚝 지방흡입</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Arm Liposuction</v>
+      </c>
+      <c r="F103" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G103" t="str">
+        <v>liposuction</v>
+      </c>
+      <c r="H103" t="str">
+        <v>arm</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>body</v>
+      </c>
+      <c r="B104" t="str">
+        <v>CT091</v>
+      </c>
+      <c r="C104" t="str">
+        <v>lipo_calf</v>
+      </c>
+      <c r="D104" t="str">
+        <v>종아리 지방흡입</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Calf Liposuction</v>
+      </c>
+      <c r="F104" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G104" t="str">
+        <v>liposuction</v>
+      </c>
+      <c r="H104" t="str">
+        <v>calf</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>body</v>
+      </c>
+      <c r="B105" t="str">
+        <v>CT092</v>
+      </c>
+      <c r="C105" t="str">
+        <v>lipo_chest_male</v>
+      </c>
+      <c r="D105" t="str">
+        <v>남성 여유증 (가슴)</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Gynecomastia</v>
+      </c>
+      <c r="F105" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G105" t="str">
+        <v>liposuction</v>
+      </c>
+      <c r="H105" t="str">
+        <v>chest</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>body</v>
+      </c>
+      <c r="B106" t="str">
+        <v>CT093</v>
+      </c>
+      <c r="C106" t="str">
+        <v>lipo_revision</v>
+      </c>
+      <c r="D106" t="str">
+        <v>재수술 지방흡입</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Revision Liposuction</v>
+      </c>
+      <c r="F106" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G106" t="str">
+        <v>liposuction</v>
+      </c>
+      <c r="H106" t="str">
+        <v>body</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>body</v>
+      </c>
+      <c r="B107" t="str">
+        <v>CT094</v>
+      </c>
+      <c r="C107" t="str">
+        <v>lipo_lams</v>
+      </c>
+      <c r="D107" t="str">
+        <v>람스 (LAMS)</v>
+      </c>
+      <c r="E107" t="str">
+        <v>LAMS (365mc Proprietary)</v>
+      </c>
+      <c r="F107" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G107" t="str">
+        <v>liposuction</v>
+      </c>
+      <c r="H107" t="str">
+        <v>body</v>
+      </c>
+      <c r="I107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>body</v>
+      </c>
+      <c r="B108" t="str">
+        <v>CT095</v>
+      </c>
+      <c r="C108" t="str">
+        <v>lipo_general</v>
+      </c>
+      <c r="D108" t="str">
+        <v>지방흡입 (일반)</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Liposuction (Generic)</v>
+      </c>
+      <c r="F108" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G108" t="str">
+        <v>liposuction</v>
+      </c>
+      <c r="H108" t="str">
+        <v>body</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>body</v>
+      </c>
+      <c r="B109" t="str">
+        <v>CT096</v>
+      </c>
+      <c r="C109" t="str">
+        <v>accusculpt</v>
+      </c>
+      <c r="D109" t="str">
+        <v>아큐스컬프 (Accusculpt)</v>
+      </c>
+      <c r="E109" t="str">
+        <v>Accusculpt (Laser Lipo)</v>
+      </c>
+      <c r="F109" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G109" t="str">
+        <v>laser_ablative</v>
+      </c>
+      <c r="H109" t="str">
+        <v>face,body</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>body</v>
+      </c>
+      <c r="B110" t="str">
+        <v>CT097</v>
+      </c>
+      <c r="C110" t="str">
+        <v>fat_grafting</v>
+      </c>
+      <c r="D110" t="str">
+        <v>지방이식 (자가지방)</v>
+      </c>
+      <c r="E110" t="str">
+        <v>Autologous Fat Grafting</v>
+      </c>
+      <c r="F110" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G110" t="str">
+        <v>fat_grafting</v>
+      </c>
+      <c r="H110" t="str">
+        <v>face,breast,body</v>
+      </c>
+      <c r="I110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>body</v>
+      </c>
+      <c r="B111" t="str">
+        <v>CT098</v>
+      </c>
+      <c r="C111" t="str">
+        <v>body_emsculpt</v>
+      </c>
+      <c r="D111" t="str">
+        <v>엠스컬프 (Emsculpt)</v>
+      </c>
+      <c r="E111" t="str">
+        <v>EM Muscle Stimulation (Emsculpt)</v>
+      </c>
+      <c r="F111" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G111" t="str">
+        <v>em_muscle_stim</v>
+      </c>
+      <c r="H111" t="str">
+        <v>body,abdomen,buttocks,arm,thigh</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>body</v>
+      </c>
+      <c r="B112" t="str">
+        <v>CT120</v>
+      </c>
+      <c r="C112" t="str">
+        <v>surgery_breast_aug</v>
+      </c>
+      <c r="D112" t="str">
+        <v>가슴 확대</v>
+      </c>
+      <c r="E112" t="str">
+        <v>Breast Augmentation</v>
+      </c>
+      <c r="F112" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G112" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H112" t="str">
+        <v>breast</v>
+      </c>
+      <c r="I112">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>body</v>
+      </c>
+      <c r="B113" t="str">
+        <v>CT121</v>
+      </c>
+      <c r="C113" t="str">
+        <v>surgery_breast_red</v>
+      </c>
+      <c r="D113" t="str">
+        <v>가슴 축소</v>
+      </c>
+      <c r="E113" t="str">
+        <v>Breast Reduction</v>
+      </c>
+      <c r="F113" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G113" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H113" t="str">
+        <v>breast</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>body</v>
+      </c>
+      <c r="B114" t="str">
+        <v>CT139</v>
+      </c>
+      <c r="C114" t="str">
+        <v>surgery_hip_aug</v>
+      </c>
+      <c r="D114" t="str">
+        <v>힙업 (Hip Augmentation)</v>
+      </c>
+      <c r="E114" t="str">
+        <v>Hip Augmentation</v>
+      </c>
+      <c r="F114" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G114" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H114" t="str">
+        <v>buttocks</v>
+      </c>
+      <c r="I114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>body</v>
+      </c>
+      <c r="B115" t="str">
+        <v>CT140</v>
+      </c>
+      <c r="C115" t="str">
+        <v>surgery_hip_dip</v>
+      </c>
+      <c r="D115" t="str">
+        <v>힙딥 교정</v>
+      </c>
+      <c r="E115" t="str">
+        <v>Hip Dip Correction</v>
+      </c>
+      <c r="F115" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G115" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H115" t="str">
+        <v>buttocks,hip</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>body</v>
+      </c>
+      <c r="B116" t="str">
+        <v>CT141</v>
+      </c>
+      <c r="C116" t="str">
+        <v>surgery_abdomen</v>
+      </c>
+      <c r="D116" t="str">
+        <v>복부성형</v>
+      </c>
+      <c r="E116" t="str">
+        <v>Abdominoplasty</v>
+      </c>
+      <c r="F116" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G116" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H116" t="str">
+        <v>abdomen</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B117" t="str">
+        <v>CT021</v>
+      </c>
+      <c r="C117" t="str">
+        <v>laser_co2</v>
+      </c>
+      <c r="D117" t="str">
+        <v>CO2 레이저</v>
+      </c>
+      <c r="E117" t="str">
+        <v>CO2 Laser</v>
+      </c>
+      <c r="F117" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G117" t="str">
+        <v>laser_ablative</v>
+      </c>
+      <c r="H117" t="str">
+        <v>face,skin</v>
+      </c>
+      <c r="I117">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B118" t="str">
+        <v>CT022</v>
+      </c>
+      <c r="C118" t="str">
+        <v>laser_fraxel</v>
+      </c>
+      <c r="D118" t="str">
+        <v>프락셀 (Fraxel)</v>
+      </c>
+      <c r="E118" t="str">
+        <v>Fraxel Laser</v>
+      </c>
+      <c r="F118" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G118" t="str">
+        <v>laser_ablative</v>
+      </c>
+      <c r="H118" t="str">
+        <v>face,skin</v>
+      </c>
+      <c r="I118">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B119" t="str">
+        <v>CT023</v>
+      </c>
+      <c r="C119" t="str">
+        <v>laser_pico</v>
+      </c>
+      <c r="D119" t="str">
+        <v>피코 레이저 (Pico)</v>
+      </c>
+      <c r="E119" t="str">
+        <v>Pico Laser</v>
+      </c>
+      <c r="F119" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G119" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H119" t="str">
+        <v>face,skin</v>
+      </c>
+      <c r="I119">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B120" t="str">
+        <v>CT024</v>
+      </c>
+      <c r="C120" t="str">
+        <v>laser_genesis</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Laser Genesis</v>
+      </c>
+      <c r="E120" t="str">
+        <v>Laser Genesis</v>
+      </c>
+      <c r="F120" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G120" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H120" t="str">
+        <v>face</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B121" t="str">
+        <v>CT025</v>
+      </c>
+      <c r="C121" t="str">
+        <v>laser_reepot</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Reepot</v>
+      </c>
+      <c r="E121" t="str">
+        <v>Reepot</v>
+      </c>
+      <c r="F121" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G121" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H121" t="str">
+        <v>face</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B122" t="str">
+        <v>CT026</v>
+      </c>
+      <c r="C122" t="str">
+        <v>laser_lucas</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Lucas Plus</v>
+      </c>
+      <c r="E122" t="str">
+        <v>Lucas Plus</v>
+      </c>
+      <c r="F122" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G122" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H122" t="str">
+        <v>face</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B123" t="str">
+        <v>CT027</v>
+      </c>
+      <c r="C123" t="str">
+        <v>laser_drt</v>
+      </c>
+      <c r="D123" t="str">
+        <v>DRT</v>
+      </c>
+      <c r="E123" t="str">
+        <v>DRT Laser</v>
+      </c>
+      <c r="F123" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G123" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H123" t="str">
+        <v>face</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B124" t="str">
+        <v>CT028</v>
+      </c>
+      <c r="C124" t="str">
+        <v>laser_mirajet</v>
+      </c>
+      <c r="D124" t="str">
+        <v>미라젯</v>
+      </c>
+      <c r="E124" t="str">
+        <v>Mirajet</v>
+      </c>
+      <c r="F124" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G124" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H124" t="str">
+        <v>face</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B125" t="str">
+        <v>CT029</v>
+      </c>
+      <c r="C125" t="str">
+        <v>laser_excelv</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Excel V</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Excel V (Vascular Laser)</v>
+      </c>
+      <c r="F125" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G125" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H125" t="str">
+        <v>face</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B126" t="str">
+        <v>CT030</v>
+      </c>
+      <c r="C126" t="str">
+        <v>laser_bbl</v>
+      </c>
+      <c r="D126" t="str">
+        <v>BBL</v>
+      </c>
+      <c r="E126" t="str">
+        <v>BBL (IPL)</v>
+      </c>
+      <c r="F126" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G126" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H126" t="str">
+        <v>face</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B127" t="str">
+        <v>CT031</v>
+      </c>
+      <c r="C127" t="str">
+        <v>laser_ipl</v>
+      </c>
+      <c r="D127" t="str">
+        <v>IPL</v>
+      </c>
+      <c r="E127" t="str">
+        <v>IPL</v>
+      </c>
+      <c r="F127" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G127" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H127" t="str">
+        <v>face</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B128" t="str">
+        <v>CT032</v>
+      </c>
+      <c r="C128" t="str">
+        <v>laser_photona</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Photona</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Photona</v>
+      </c>
+      <c r="F128" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G128" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H128" t="str">
+        <v>face</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B129" t="str">
+        <v>CT033</v>
+      </c>
+      <c r="C129" t="str">
+        <v>laser_dual_repair</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Dual Repair Laser</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Dual Repair Laser</v>
+      </c>
+      <c r="F129" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G129" t="str">
+        <v>laser_ablative</v>
+      </c>
+      <c r="H129" t="str">
+        <v>face,skin</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B130" t="str">
+        <v>CT034</v>
+      </c>
+      <c r="C130" t="str">
+        <v>laser_fractional</v>
+      </c>
+      <c r="D130" t="str">
+        <v>프락셔널 레이저 (Fractional)</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Fractional Laser</v>
+      </c>
+      <c r="F130" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G130" t="str">
+        <v>laser_ablative</v>
+      </c>
+      <c r="H130" t="str">
+        <v>face,skin</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B131" t="str">
+        <v>CT035</v>
+      </c>
+      <c r="C131" t="str">
+        <v>laser_whitening_generic</v>
+      </c>
+      <c r="D131" t="str">
+        <v>미백/색소 레이저 (generic)</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Whitening / Pigment Laser</v>
+      </c>
+      <c r="F131" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G131" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H131" t="str">
+        <v>face</v>
+      </c>
+      <c r="I131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B132" t="str">
+        <v>CT038</v>
+      </c>
+      <c r="C132" t="str">
+        <v>inflammation_injection</v>
+      </c>
+      <c r="D132" t="str">
+        <v>염증 주사 (스테로이드)</v>
+      </c>
+      <c r="E132" t="str">
+        <v>Inflammation Injection (Steroid)</v>
+      </c>
+      <c r="F132" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G132" t="str">
+        <v>injection_toxin</v>
+      </c>
+      <c r="H132" t="str">
+        <v>face</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B133" t="str">
+        <v>CT074</v>
+      </c>
+      <c r="C133" t="str">
+        <v>acne_extraction</v>
+      </c>
+      <c r="D133" t="str">
+        <v>여드름 압출</v>
+      </c>
+      <c r="E133" t="str">
+        <v>Acne Extraction</v>
+      </c>
+      <c r="F133" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G133" t="str">
+        <v>extraction</v>
+      </c>
+      <c r="H133" t="str">
+        <v>face</v>
+      </c>
+      <c r="I133">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B134" t="str">
+        <v>CT075</v>
+      </c>
+      <c r="C134" t="str">
+        <v>acne_pdt</v>
+      </c>
+      <c r="D134" t="str">
+        <v>PDT (광역동 치료)</v>
+      </c>
+      <c r="E134" t="str">
+        <v>PDT (Photodynamic)</v>
+      </c>
+      <c r="F134" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G134" t="str">
+        <v>topical</v>
+      </c>
+      <c r="H134" t="str">
+        <v>face</v>
+      </c>
+      <c r="I134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B135" t="str">
+        <v>CT076</v>
+      </c>
+      <c r="C135" t="str">
+        <v>acne_concern_generic</v>
+      </c>
+      <c r="D135" t="str">
+        <v>여드름 케어 (generic)</v>
+      </c>
+      <c r="E135" t="str">
+        <v>Acne Care (Generic)</v>
+      </c>
+      <c r="F135" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G135" t="str">
+        <v>extraction</v>
+      </c>
+      <c r="H135" t="str">
+        <v>face</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B136" t="str">
+        <v>CT077</v>
+      </c>
+      <c r="C136" t="str">
+        <v>scar_subcision</v>
+      </c>
+      <c r="D136" t="str">
+        <v>서브시전 (Subcision)</v>
+      </c>
+      <c r="E136" t="str">
+        <v>Subcision (Acne Scar)</v>
+      </c>
+      <c r="F136" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G136" t="str">
+        <v>subcision</v>
+      </c>
+      <c r="H136" t="str">
+        <v>face</v>
+      </c>
+      <c r="I136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B137" t="str">
+        <v>CT078</v>
+      </c>
+      <c r="C137" t="str">
+        <v>pigmentation_care</v>
+      </c>
+      <c r="D137" t="str">
+        <v>잡티/기미 케어</v>
+      </c>
+      <c r="E137" t="str">
+        <v>Pigmentation Care</v>
+      </c>
+      <c r="F137" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G137" t="str">
+        <v>laser_non_ablative</v>
+      </c>
+      <c r="H137" t="str">
+        <v>face</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B138" t="str">
+        <v>CT079</v>
+      </c>
+      <c r="C138" t="str">
+        <v>pore_scar_care</v>
+      </c>
+      <c r="D138" t="str">
+        <v>모공/여드름흉터 케어</v>
+      </c>
+      <c r="E138" t="str">
+        <v>Pore / Scar Care</v>
+      </c>
+      <c r="F138" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G138" t="str">
+        <v>rf</v>
+      </c>
+      <c r="H138" t="str">
+        <v>face</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>skin</v>
+      </c>
+      <c r="B139" t="str">
+        <v>CT137</v>
+      </c>
+      <c r="C139" t="str">
+        <v>surgery_benign</v>
+      </c>
+      <c r="D139" t="str">
+        <v>양성종양·모반 제거</v>
+      </c>
+      <c r="E139" t="str">
+        <v>Benign Lesion Removal</v>
+      </c>
+      <c r="F139" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G139" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="H139" t="str">
+        <v>skin</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>hair</v>
+      </c>
+      <c r="B140" t="str">
+        <v>CT059</v>
+      </c>
+      <c r="C140" t="str">
+        <v>exosome_asce</v>
+      </c>
+      <c r="D140" t="str">
+        <v>ASCE+ 엑소좀</v>
+      </c>
+      <c r="E140" t="str">
+        <v>Exosome (ASCE+)</v>
+      </c>
+      <c r="F140" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G140" t="str">
+        <v>exosome</v>
+      </c>
+      <c r="H140" t="str">
+        <v>face,scalp</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>hair</v>
+      </c>
+      <c r="B141" t="str">
+        <v>CT082</v>
+      </c>
+      <c r="C141" t="str">
+        <v>stemcell_hair</v>
+      </c>
+      <c r="D141" t="str">
+        <v>줄기세포 탈모 케어</v>
+      </c>
+      <c r="E141" t="str">
+        <v>Hair Stem Cell</v>
+      </c>
+      <c r="F141" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G141" t="str">
+        <v>stem_cell</v>
+      </c>
+      <c r="H141" t="str">
+        <v>scalp</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>hair</v>
+      </c>
+      <c r="B142" t="str">
+        <v>CT086</v>
+      </c>
+      <c r="C142" t="str">
+        <v>prp</v>
+      </c>
+      <c r="D142" t="str">
+        <v>PRP (자가혈)</v>
+      </c>
+      <c r="E142" t="str">
+        <v>PRP</v>
+      </c>
+      <c r="F142" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G142" t="str">
+        <v>prp</v>
+      </c>
+      <c r="H142" t="str">
+        <v>face,scalp</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>hair</v>
+      </c>
+      <c r="B143" t="str">
+        <v>CT144</v>
+      </c>
+      <c r="C143" t="str">
+        <v>hair_transplant</v>
+      </c>
+      <c r="D143" t="str">
+        <v>모발이식 (FUE)</v>
+      </c>
+      <c r="E143" t="str">
+        <v>Hair Transplant</v>
+      </c>
+      <c r="F143" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G143" t="str">
+        <v>hair_transplant</v>
+      </c>
+      <c r="H143" t="str">
+        <v>scalp</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>wellness</v>
+      </c>
+      <c r="B144" t="str">
+        <v>CT065</v>
+      </c>
+      <c r="C144" t="str">
+        <v>iv_therapy</v>
+      </c>
+      <c r="D144" t="str">
+        <v>IV 수액/영양주사</v>
+      </c>
+      <c r="E144" t="str">
+        <v>IV Therapy / Functional</v>
+      </c>
+      <c r="F144" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G144" t="str">
+        <v>iv_therapy</v>
+      </c>
+      <c r="H144" t="str">
+        <v>systemic</v>
+      </c>
+      <c r="I144">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>wellness</v>
+      </c>
+      <c r="B145" t="str">
+        <v>CT083</v>
+      </c>
+      <c r="C145" t="str">
+        <v>stemcell_bio</v>
+      </c>
+      <c r="D145" t="str">
+        <v>바이오샷 (전신)</v>
+      </c>
+      <c r="E145" t="str">
+        <v>Bio Stem Cell (Systemic)</v>
+      </c>
+      <c r="F145" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G145" t="str">
+        <v>stem_cell</v>
+      </c>
+      <c r="H145" t="str">
+        <v>systemic</v>
+      </c>
+      <c r="I145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>wellness</v>
+      </c>
+      <c r="B146" t="str">
+        <v>CT084</v>
+      </c>
+      <c r="C146" t="str">
+        <v>stemcell_banking</v>
+      </c>
+      <c r="D146" t="str">
+        <v>줄기세포 뱅킹</v>
+      </c>
+      <c r="E146" t="str">
+        <v>Stem Cell Banking</v>
+      </c>
+      <c r="F146" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G146" t="str">
+        <v>stem_cell</v>
+      </c>
+      <c r="H146" t="str">
+        <v>systemic</v>
+      </c>
+      <c r="I146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>wellness</v>
+      </c>
+      <c r="B147" t="str">
+        <v>CT085</v>
+      </c>
+      <c r="C147" t="str">
+        <v>stemcell_joint</v>
+      </c>
+      <c r="D147" t="str">
+        <v>관절 줄기세포</v>
+      </c>
+      <c r="E147" t="str">
+        <v>Joint Stem Cell</v>
+      </c>
+      <c r="F147" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G147" t="str">
+        <v>stem_cell</v>
+      </c>
+      <c r="H147" t="str">
+        <v>joint</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>wellness</v>
+      </c>
+      <c r="B148" t="str">
+        <v>CT100</v>
+      </c>
+      <c r="C148" t="str">
+        <v>cream_firming</v>
+      </c>
+      <c r="D148" t="str">
+        <v>팽팽크림 (TOPICAL)</v>
+      </c>
+      <c r="E148" t="str">
+        <v>Firming Cream (Topical)</v>
+      </c>
+      <c r="F148" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G148" t="str">
+        <v>topical</v>
+      </c>
+      <c r="H148" t="str">
+        <v>body</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>wellness</v>
+      </c>
+      <c r="B149" t="str">
+        <v>CT145</v>
+      </c>
+      <c r="C149" t="str">
+        <v>special_hyperbaric</v>
+      </c>
+      <c r="D149" t="str">
+        <v>고압산소 치료</v>
+      </c>
+      <c r="E149" t="str">
+        <v>Hyperbaric Oxygen Therapy</v>
+      </c>
+      <c r="F149" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G149" t="str">
+        <v>iv_therapy</v>
+      </c>
+      <c r="H149" t="str">
+        <v>systemic</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>wellness</v>
+      </c>
+      <c r="B150" t="str">
+        <v>CT148</v>
+      </c>
+      <c r="C150" t="str">
+        <v>bundle_salondrtunes_sportif</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Salon de Sportif (다이어트/산후/경기력)</v>
+      </c>
+      <c r="E150" t="str">
+        <v>Salon de Sportif (Diet / Postpartum / Performance)</v>
+      </c>
+      <c r="F150" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G150" t="str">
+        <v>iv_therapy</v>
+      </c>
+      <c r="H150" t="str">
+        <v>systemic,body</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B151" t="str">
+        <v>CT149</v>
+      </c>
+      <c r="C151" t="str">
+        <v>dental_implant_oneday</v>
+      </c>
+      <c r="D151" t="str">
+        <v>원데이 임플란트</v>
+      </c>
+      <c r="E151" t="str">
+        <v>One-day Implant</v>
+      </c>
+      <c r="F151" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G151" t="str">
+        <v>implant</v>
+      </c>
+      <c r="H151" t="str">
+        <v>dental</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B152" t="str">
+        <v>CT150</v>
+      </c>
+      <c r="C152" t="str">
+        <v>dental_implant_sleep</v>
+      </c>
+      <c r="D152" t="str">
+        <v>수면 임플란트</v>
+      </c>
+      <c r="E152" t="str">
+        <v>Sleep Implant (Sedation)</v>
+      </c>
+      <c r="F152" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G152" t="str">
+        <v>implant</v>
+      </c>
+      <c r="H152" t="str">
+        <v>dental</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B153" t="str">
+        <v>CT151</v>
+      </c>
+      <c r="C153" t="str">
+        <v>dental_implant_general</v>
+      </c>
+      <c r="D153" t="str">
+        <v>일반 임플란트</v>
+      </c>
+      <c r="E153" t="str">
+        <v>Standard Implant</v>
+      </c>
+      <c r="F153" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G153" t="str">
+        <v>implant</v>
+      </c>
+      <c r="H153" t="str">
+        <v>dental</v>
+      </c>
+      <c r="I153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B154" t="str">
+        <v>CT152</v>
+      </c>
+      <c r="C154" t="str">
+        <v>dental_laminate</v>
+      </c>
+      <c r="D154" t="str">
+        <v>라미네이트 (Veneer)</v>
+      </c>
+      <c r="E154" t="str">
+        <v>Veneer (Laminate)</v>
+      </c>
+      <c r="F154" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G154" t="str">
+        <v>prosthetic</v>
+      </c>
+      <c r="H154" t="str">
+        <v>dental</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B155" t="str">
+        <v>CT153</v>
+      </c>
+      <c r="C155" t="str">
+        <v>dental_whitening</v>
+      </c>
+      <c r="D155" t="str">
+        <v>치아 미백</v>
+      </c>
+      <c r="E155" t="str">
+        <v>Teeth Whitening</v>
+      </c>
+      <c r="F155" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G155" t="str">
+        <v>bleaching_dental</v>
+      </c>
+      <c r="H155" t="str">
+        <v>dental</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B156" t="str">
+        <v>CT154</v>
+      </c>
+      <c r="C156" t="str">
+        <v>dental_gum_contour</v>
+      </c>
+      <c r="D156" t="str">
+        <v>잇몸 성형</v>
+      </c>
+      <c r="E156" t="str">
+        <v>Gum Contouring</v>
+      </c>
+      <c r="F156" t="str">
+        <v>surgery</v>
+      </c>
+      <c r="G156" t="str">
+        <v>periodontal</v>
+      </c>
+      <c r="H156" t="str">
+        <v>dental</v>
+      </c>
+      <c r="I156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B157" t="str">
+        <v>CT155</v>
+      </c>
+      <c r="C157" t="str">
+        <v>dental_ortho_invisalign</v>
+      </c>
+      <c r="D157" t="str">
+        <v>인비절라인 (Invisalign)</v>
+      </c>
+      <c r="E157" t="str">
+        <v>Invisalign</v>
+      </c>
+      <c r="F157" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G157" t="str">
+        <v>orthodontic</v>
+      </c>
+      <c r="H157" t="str">
+        <v>dental</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B158" t="str">
+        <v>CT156</v>
+      </c>
+      <c r="C158" t="str">
+        <v>dental_ortho_partial</v>
+      </c>
+      <c r="D158" t="str">
+        <v>부분교정</v>
+      </c>
+      <c r="E158" t="str">
+        <v>Partial Orthodontics</v>
+      </c>
+      <c r="F158" t="str">
+        <v>petit</v>
+      </c>
+      <c r="G158" t="str">
+        <v>orthodontic</v>
+      </c>
+      <c r="H158" t="str">
+        <v>dental</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B159" t="str">
+        <v>CT157</v>
+      </c>
+      <c r="C159" t="str">
+        <v>dental_caries</v>
+      </c>
+      <c r="D159" t="str">
+        <v>충치 치료</v>
+      </c>
+      <c r="E159" t="str">
+        <v>Caries Restoration</v>
+      </c>
+      <c r="F159" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G159" t="str">
+        <v>restorative</v>
+      </c>
+      <c r="H159" t="str">
+        <v>dental</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>dental</v>
+      </c>
+      <c r="B160" t="str">
+        <v>CT158</v>
+      </c>
+      <c r="C160" t="str">
+        <v>dental_scaling</v>
+      </c>
+      <c r="D160" t="str">
+        <v>스케일링 (치과)</v>
+      </c>
+      <c r="E160" t="str">
+        <v>Dental Scaling</v>
+      </c>
+      <c r="F160" t="str">
+        <v>skin</v>
+      </c>
+      <c r="G160" t="str">
+        <v>periodontal</v>
+      </c>
+      <c r="H160" t="str">
+        <v>dental</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I160"/>
+  </ignoredErrors>
+</worksheet>
 </file>